--- a/sales_analytics_template.xlsx
+++ b/sales_analytics_template.xlsx
@@ -268,7 +268,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +339,22 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9DFC2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -367,21 +383,21 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF2F5233"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,7 +407,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
@@ -402,18 +418,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -433,6 +443,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F5233"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF4C7A47"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4C7A47"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
       </bottom>
       <diagonal/>
     </border>
@@ -462,7 +496,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -507,23 +541,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,7 +623,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFEFF5EC"/>
+      <rgbColor rgb="FFC9DFC2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -576,7 +638,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDCEAD5"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -593,11 +655,11 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF4C7A47"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -664,10 +726,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -746,11 +810,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60626891"/>
-        <c:axId val="71444206"/>
+        <c:axId val="85478628"/>
+        <c:axId val="33340350"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60626891"/>
+        <c:axId val="85478628"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -782,7 +846,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71444206"/>
+        <c:crossAx val="33340350"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -790,7 +854,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71444206"/>
+        <c:axId val="33340350"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -866,7 +930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60626891"/>
+        <c:crossAx val="85478628"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -979,10 +1043,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1103,11 +1169,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70516394"/>
-        <c:axId val="99513371"/>
+        <c:axId val="83605963"/>
+        <c:axId val="89831716"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70516394"/>
+        <c:axId val="83605963"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1139,7 +1205,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99513371"/>
+        <c:crossAx val="89831716"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1147,7 +1213,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99513371"/>
+        <c:axId val="89831716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1223,7 +1289,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70516394"/>
+        <c:crossAx val="83605963"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1414,12 +1480,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -1438,12 +1505,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -1462,12 +1530,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -1486,12 +1555,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -1510,12 +1580,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -1534,12 +1605,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -1556,12 +1628,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1729,10 +1802,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1802,11 +1877,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74077153"/>
-        <c:axId val="79109008"/>
+        <c:axId val="44869790"/>
+        <c:axId val="20786432"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74077153"/>
+        <c:axId val="44869790"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1838,7 +1913,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79109008"/>
+        <c:crossAx val="20786432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1846,7 +1921,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79109008"/>
+        <c:axId val="20786432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1922,7 +1997,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74077153"/>
+        <c:crossAx val="44869790"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2102,12 +2177,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -2126,12 +2202,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -2150,12 +2227,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -2174,12 +2252,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -2198,12 +2277,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -2220,12 +2300,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -2332,14 +2413,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>26640</xdr:rowOff>
+      <xdr:rowOff>41040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2347,7 +2428,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="13430160" y="762120"/>
+        <a:off x="13430160" y="1038240"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2367,14 +2448,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>365400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2382,7 +2463,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="1800360"/>
+        <a:off x="4444920" y="2104920"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2397,14 +2478,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>481680</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2412,7 +2493,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="4657680"/>
+        <a:off x="4444920" y="4962600"/>
         <a:ext cx="3599640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2427,14 +2508,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>442800</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2442,7 +2523,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="6562800"/>
+        <a:off x="4444920" y="6867360"/>
         <a:ext cx="4319640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2457,14 +2538,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>481680</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2472,7 +2553,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="8467560"/>
+        <a:off x="4444920" y="8772480"/>
         <a:ext cx="3599640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6327,44 +6408,46 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="14" t="s">
         <v>39</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -6372,42 +6455,42 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="str">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="str">
         <f aca="false">IF(A6="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A6))</f>
         <v/>
       </c>
-      <c r="D6" s="10" t="str">
+      <c r="D6" s="16" t="str">
         <f aca="false">IF(A6="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A6))</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="str">
+      <c r="E6" s="15" t="str">
         <f aca="false">IF(A6="","",RANK(D6,$D$6:$D$35)+COUNTIF($D$6:D6,D6)-1)</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="str">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15" t="str">
         <f aca="false">IF(A7="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A7))</f>
         <v/>
       </c>
-      <c r="D7" s="10" t="str">
+      <c r="D7" s="16" t="str">
         <f aca="false">IF(A7="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A7))</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="str">
+      <c r="E7" s="15" t="str">
         <f aca="false">IF(A7="","",RANK(D7,$D$6:$D$35)+COUNTIF($D$6:D7,D7)-1)</f>
         <v/>
       </c>
@@ -6418,23 +6501,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(1,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I7" s="11" t="str">
+      <c r="I7" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(1,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9" t="str">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="str">
         <f aca="false">IF(A8="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A8))</f>
         <v/>
       </c>
-      <c r="D8" s="10" t="str">
+      <c r="D8" s="16" t="str">
         <f aca="false">IF(A8="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A8))</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="15" t="str">
         <f aca="false">IF(A8="","",RANK(D8,$D$6:$D$35)+COUNTIF($D$6:D8,D8)-1)</f>
         <v/>
       </c>
@@ -6445,23 +6528,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(2,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I8" s="11" t="str">
+      <c r="I8" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(2,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="str">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15" t="str">
         <f aca="false">IF(A9="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A9))</f>
         <v/>
       </c>
-      <c r="D9" s="10" t="str">
+      <c r="D9" s="16" t="str">
         <f aca="false">IF(A9="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A9))</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="15" t="str">
         <f aca="false">IF(A9="","",RANK(D9,$D$6:$D$35)+COUNTIF($D$6:D9,D9)-1)</f>
         <v/>
       </c>
@@ -6472,23 +6555,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(3,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I9" s="11" t="str">
+      <c r="I9" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(3,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="str">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15" t="str">
         <f aca="false">IF(A10="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A10))</f>
         <v/>
       </c>
-      <c r="D10" s="10" t="str">
+      <c r="D10" s="16" t="str">
         <f aca="false">IF(A10="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A10))</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="str">
+      <c r="E10" s="15" t="str">
         <f aca="false">IF(A10="","",RANK(D10,$D$6:$D$35)+COUNTIF($D$6:D10,D10)-1)</f>
         <v/>
       </c>
@@ -6499,23 +6582,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(4,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I10" s="11" t="str">
+      <c r="I10" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(4,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="str">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15" t="str">
         <f aca="false">IF(A11="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A11))</f>
         <v/>
       </c>
-      <c r="D11" s="10" t="str">
+      <c r="D11" s="16" t="str">
         <f aca="false">IF(A11="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A11))</f>
         <v/>
       </c>
-      <c r="E11" s="9" t="str">
+      <c r="E11" s="15" t="str">
         <f aca="false">IF(A11="","",RANK(D11,$D$6:$D$35)+COUNTIF($D$6:D11,D11)-1)</f>
         <v/>
       </c>
@@ -6526,23 +6609,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(5,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I11" s="11" t="str">
+      <c r="I11" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(5,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9" t="str">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15" t="str">
         <f aca="false">IF(A12="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A12))</f>
         <v/>
       </c>
-      <c r="D12" s="10" t="str">
+      <c r="D12" s="16" t="str">
         <f aca="false">IF(A12="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A12))</f>
         <v/>
       </c>
-      <c r="E12" s="9" t="str">
+      <c r="E12" s="15" t="str">
         <f aca="false">IF(A12="","",RANK(D12,$D$6:$D$35)+COUNTIF($D$6:D12,D12)-1)</f>
         <v/>
       </c>
@@ -6553,23 +6636,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(6,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I12" s="11" t="str">
+      <c r="I12" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(6,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9" t="str">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15" t="str">
         <f aca="false">IF(A13="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A13))</f>
         <v/>
       </c>
-      <c r="D13" s="10" t="str">
+      <c r="D13" s="16" t="str">
         <f aca="false">IF(A13="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A13))</f>
         <v/>
       </c>
-      <c r="E13" s="9" t="str">
+      <c r="E13" s="15" t="str">
         <f aca="false">IF(A13="","",RANK(D13,$D$6:$D$35)+COUNTIF($D$6:D13,D13)-1)</f>
         <v/>
       </c>
@@ -6580,23 +6663,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(7,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I13" s="11" t="str">
+      <c r="I13" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(7,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="str">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15" t="str">
         <f aca="false">IF(A14="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A14))</f>
         <v/>
       </c>
-      <c r="D14" s="10" t="str">
+      <c r="D14" s="16" t="str">
         <f aca="false">IF(A14="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A14))</f>
         <v/>
       </c>
-      <c r="E14" s="9" t="str">
+      <c r="E14" s="15" t="str">
         <f aca="false">IF(A14="","",RANK(D14,$D$6:$D$35)+COUNTIF($D$6:D14,D14)-1)</f>
         <v/>
       </c>
@@ -6607,23 +6690,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(8,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I14" s="11" t="str">
+      <c r="I14" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(8,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9" t="str">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15" t="str">
         <f aca="false">IF(A15="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A15))</f>
         <v/>
       </c>
-      <c r="D15" s="10" t="str">
+      <c r="D15" s="16" t="str">
         <f aca="false">IF(A15="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A15))</f>
         <v/>
       </c>
-      <c r="E15" s="9" t="str">
+      <c r="E15" s="15" t="str">
         <f aca="false">IF(A15="","",RANK(D15,$D$6:$D$35)+COUNTIF($D$6:D15,D15)-1)</f>
         <v/>
       </c>
@@ -6634,23 +6717,23 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(9,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I15" s="11" t="str">
+      <c r="I15" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(9,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="str">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15" t="str">
         <f aca="false">IF(A16="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A16))</f>
         <v/>
       </c>
-      <c r="D16" s="10" t="str">
+      <c r="D16" s="16" t="str">
         <f aca="false">IF(A16="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A16))</f>
         <v/>
       </c>
-      <c r="E16" s="9" t="str">
+      <c r="E16" s="15" t="str">
         <f aca="false">IF(A16="","",RANK(D16,$D$6:$D$35)+COUNTIF($D$6:D16,D16)-1)</f>
         <v/>
       </c>
@@ -6661,311 +6744,311 @@
         <f aca="false">IFERROR(INDEX('Product Performance'!$A$6:$A$35,MATCH(10,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="11" t="str">
+      <c r="I16" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Product Performance'!$D$6:$D$35,MATCH(10,'Product Performance'!$E$6:$E$35,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9" t="str">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15" t="str">
         <f aca="false">IF(A17="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A17))</f>
         <v/>
       </c>
-      <c r="D17" s="10" t="str">
+      <c r="D17" s="16" t="str">
         <f aca="false">IF(A17="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A17))</f>
         <v/>
       </c>
-      <c r="E17" s="9" t="str">
+      <c r="E17" s="15" t="str">
         <f aca="false">IF(A17="","",RANK(D17,$D$6:$D$35)+COUNTIF($D$6:D17,D17)-1)</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9" t="str">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15" t="str">
         <f aca="false">IF(A18="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A18))</f>
         <v/>
       </c>
-      <c r="D18" s="10" t="str">
+      <c r="D18" s="16" t="str">
         <f aca="false">IF(A18="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A18))</f>
         <v/>
       </c>
-      <c r="E18" s="9" t="str">
+      <c r="E18" s="15" t="str">
         <f aca="false">IF(A18="","",RANK(D18,$D$6:$D$35)+COUNTIF($D$6:D18,D18)-1)</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9" t="str">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15" t="str">
         <f aca="false">IF(A19="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A19))</f>
         <v/>
       </c>
-      <c r="D19" s="10" t="str">
+      <c r="D19" s="16" t="str">
         <f aca="false">IF(A19="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A19))</f>
         <v/>
       </c>
-      <c r="E19" s="9" t="str">
+      <c r="E19" s="15" t="str">
         <f aca="false">IF(A19="","",RANK(D19,$D$6:$D$35)+COUNTIF($D$6:D19,D19)-1)</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9" t="str">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15" t="str">
         <f aca="false">IF(A20="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A20))</f>
         <v/>
       </c>
-      <c r="D20" s="10" t="str">
+      <c r="D20" s="16" t="str">
         <f aca="false">IF(A20="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A20))</f>
         <v/>
       </c>
-      <c r="E20" s="9" t="str">
+      <c r="E20" s="15" t="str">
         <f aca="false">IF(A20="","",RANK(D20,$D$6:$D$35)+COUNTIF($D$6:D20,D20)-1)</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9" t="str">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15" t="str">
         <f aca="false">IF(A21="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A21))</f>
         <v/>
       </c>
-      <c r="D21" s="10" t="str">
+      <c r="D21" s="16" t="str">
         <f aca="false">IF(A21="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A21))</f>
         <v/>
       </c>
-      <c r="E21" s="9" t="str">
+      <c r="E21" s="15" t="str">
         <f aca="false">IF(A21="","",RANK(D21,$D$6:$D$35)+COUNTIF($D$6:D21,D21)-1)</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9" t="str">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15" t="str">
         <f aca="false">IF(A22="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A22))</f>
         <v/>
       </c>
-      <c r="D22" s="10" t="str">
+      <c r="D22" s="16" t="str">
         <f aca="false">IF(A22="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A22))</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="str">
+      <c r="E22" s="15" t="str">
         <f aca="false">IF(A22="","",RANK(D22,$D$6:$D$35)+COUNTIF($D$6:D22,D22)-1)</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9" t="str">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15" t="str">
         <f aca="false">IF(A23="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A23))</f>
         <v/>
       </c>
-      <c r="D23" s="10" t="str">
+      <c r="D23" s="16" t="str">
         <f aca="false">IF(A23="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A23))</f>
         <v/>
       </c>
-      <c r="E23" s="9" t="str">
+      <c r="E23" s="15" t="str">
         <f aca="false">IF(A23="","",RANK(D23,$D$6:$D$35)+COUNTIF($D$6:D23,D23)-1)</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="str">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15" t="str">
         <f aca="false">IF(A24="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A24))</f>
         <v/>
       </c>
-      <c r="D24" s="10" t="str">
+      <c r="D24" s="16" t="str">
         <f aca="false">IF(A24="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A24))</f>
         <v/>
       </c>
-      <c r="E24" s="9" t="str">
+      <c r="E24" s="15" t="str">
         <f aca="false">IF(A24="","",RANK(D24,$D$6:$D$35)+COUNTIF($D$6:D24,D24)-1)</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9" t="str">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15" t="str">
         <f aca="false">IF(A25="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A25))</f>
         <v/>
       </c>
-      <c r="D25" s="10" t="str">
+      <c r="D25" s="16" t="str">
         <f aca="false">IF(A25="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A25))</f>
         <v/>
       </c>
-      <c r="E25" s="9" t="str">
+      <c r="E25" s="15" t="str">
         <f aca="false">IF(A25="","",RANK(D25,$D$6:$D$35)+COUNTIF($D$6:D25,D25)-1)</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9" t="str">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15" t="str">
         <f aca="false">IF(A26="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A26))</f>
         <v/>
       </c>
-      <c r="D26" s="10" t="str">
+      <c r="D26" s="16" t="str">
         <f aca="false">IF(A26="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A26))</f>
         <v/>
       </c>
-      <c r="E26" s="9" t="str">
+      <c r="E26" s="15" t="str">
         <f aca="false">IF(A26="","",RANK(D26,$D$6:$D$35)+COUNTIF($D$6:D26,D26)-1)</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9" t="str">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15" t="str">
         <f aca="false">IF(A27="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A27))</f>
         <v/>
       </c>
-      <c r="D27" s="10" t="str">
+      <c r="D27" s="16" t="str">
         <f aca="false">IF(A27="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A27))</f>
         <v/>
       </c>
-      <c r="E27" s="9" t="str">
+      <c r="E27" s="15" t="str">
         <f aca="false">IF(A27="","",RANK(D27,$D$6:$D$35)+COUNTIF($D$6:D27,D27)-1)</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9" t="str">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15" t="str">
         <f aca="false">IF(A28="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A28))</f>
         <v/>
       </c>
-      <c r="D28" s="10" t="str">
+      <c r="D28" s="16" t="str">
         <f aca="false">IF(A28="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A28))</f>
         <v/>
       </c>
-      <c r="E28" s="9" t="str">
+      <c r="E28" s="15" t="str">
         <f aca="false">IF(A28="","",RANK(D28,$D$6:$D$35)+COUNTIF($D$6:D28,D28)-1)</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9" t="str">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15" t="str">
         <f aca="false">IF(A29="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A29))</f>
         <v/>
       </c>
-      <c r="D29" s="10" t="str">
+      <c r="D29" s="16" t="str">
         <f aca="false">IF(A29="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A29))</f>
         <v/>
       </c>
-      <c r="E29" s="9" t="str">
+      <c r="E29" s="15" t="str">
         <f aca="false">IF(A29="","",RANK(D29,$D$6:$D$35)+COUNTIF($D$6:D29,D29)-1)</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9" t="str">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15" t="str">
         <f aca="false">IF(A30="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A30))</f>
         <v/>
       </c>
-      <c r="D30" s="10" t="str">
+      <c r="D30" s="16" t="str">
         <f aca="false">IF(A30="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A30))</f>
         <v/>
       </c>
-      <c r="E30" s="9" t="str">
+      <c r="E30" s="15" t="str">
         <f aca="false">IF(A30="","",RANK(D30,$D$6:$D$35)+COUNTIF($D$6:D30,D30)-1)</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9" t="str">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15" t="str">
         <f aca="false">IF(A31="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A31))</f>
         <v/>
       </c>
-      <c r="D31" s="10" t="str">
+      <c r="D31" s="16" t="str">
         <f aca="false">IF(A31="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A31))</f>
         <v/>
       </c>
-      <c r="E31" s="9" t="str">
+      <c r="E31" s="15" t="str">
         <f aca="false">IF(A31="","",RANK(D31,$D$6:$D$35)+COUNTIF($D$6:D31,D31)-1)</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9" t="str">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15" t="str">
         <f aca="false">IF(A32="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A32))</f>
         <v/>
       </c>
-      <c r="D32" s="10" t="str">
+      <c r="D32" s="16" t="str">
         <f aca="false">IF(A32="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A32))</f>
         <v/>
       </c>
-      <c r="E32" s="9" t="str">
+      <c r="E32" s="15" t="str">
         <f aca="false">IF(A32="","",RANK(D32,$D$6:$D$35)+COUNTIF($D$6:D32,D32)-1)</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9" t="str">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15" t="str">
         <f aca="false">IF(A33="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A33))</f>
         <v/>
       </c>
-      <c r="D33" s="10" t="str">
+      <c r="D33" s="16" t="str">
         <f aca="false">IF(A33="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A33))</f>
         <v/>
       </c>
-      <c r="E33" s="9" t="str">
+      <c r="E33" s="15" t="str">
         <f aca="false">IF(A33="","",RANK(D33,$D$6:$D$35)+COUNTIF($D$6:D33,D33)-1)</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9" t="str">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15" t="str">
         <f aca="false">IF(A34="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A34))</f>
         <v/>
       </c>
-      <c r="D34" s="10" t="str">
+      <c r="D34" s="16" t="str">
         <f aca="false">IF(A34="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A34))</f>
         <v/>
       </c>
-      <c r="E34" s="9" t="str">
+      <c r="E34" s="15" t="str">
         <f aca="false">IF(A34="","",RANK(D34,$D$6:$D$35)+COUNTIF($D$6:D34,D34)-1)</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9" t="str">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15" t="str">
         <f aca="false">IF(A35="","",SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$C$3:$C$152,A35))</f>
         <v/>
       </c>
-      <c r="D35" s="10" t="str">
+      <c r="D35" s="16" t="str">
         <f aca="false">IF(A35="","",SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$C$3:$C$152,A35))</f>
         <v/>
       </c>
-      <c r="E35" s="9" t="str">
+      <c r="E35" s="15" t="str">
         <f aca="false">IF(A35="","",RANK(D35,$D$6:$D$35)+COUNTIF($D$6:D35,D35)-1)</f>
         <v/>
       </c>
@@ -6984,7 +7067,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26EE6F75-3B3C-4993-947C-5520592FF6F2}</x14:id>
+          <x14:id>{71104985-249A-41B4-A94F-BCCFC0895591}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7007,7 +7090,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26EE6F75-3B3C-4993-947C-5520592FF6F2}">
+          <x14:cfRule type="dataBar" id="{71104985-249A-41B4-A94F-BCCFC0895591}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7035,69 +7118,77 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="18" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="19" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="n">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="22" t="n">
         <f aca="false">COUNTIFS('Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$I$3:$I$152,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(A6/B6,0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="22" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$G$3:$G$152,'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
@@ -7105,10 +7196,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7116,7 +7207,7 @@
       <c r="A11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,1)</f>
         <v>0</v>
       </c>
@@ -7125,7 +7216,7 @@
       <c r="A12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,2)</f>
         <v>0</v>
       </c>
@@ -7134,7 +7225,7 @@
       <c r="A13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,3)</f>
         <v>0</v>
       </c>
@@ -7143,7 +7234,7 @@
       <c r="A14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,4)</f>
         <v>0</v>
       </c>
@@ -7152,7 +7243,7 @@
       <c r="A15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,5)</f>
         <v>0</v>
       </c>
@@ -7161,7 +7252,7 @@
       <c r="A16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,6)</f>
         <v>0</v>
       </c>
@@ -7170,7 +7261,7 @@
       <c r="A17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,7)</f>
         <v>0</v>
       </c>
@@ -7179,7 +7270,7 @@
       <c r="A18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,8)</f>
         <v>0</v>
       </c>
@@ -7188,7 +7279,7 @@
       <c r="A19" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,9)</f>
         <v>0</v>
       </c>
@@ -7197,7 +7288,7 @@
       <c r="A20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,10)</f>
         <v>0</v>
       </c>
@@ -7206,7 +7297,7 @@
       <c r="A21" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,11)</f>
         <v>0</v>
       </c>
@@ -7215,7 +7306,7 @@
       <c r="A22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$J$3:$J$152,$B$3,'Sales Transactions'!$K$3:$K$152,12)</f>
         <v>0</v>
       </c>
@@ -7226,10 +7317,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7237,7 +7328,7 @@
       <c r="A26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Apparel",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7246,7 +7337,7 @@
       <c r="A27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Accessories",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7255,7 +7346,7 @@
       <c r="A28" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Home Goods",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7264,7 +7355,7 @@
       <c r="A29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Digital",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7273,7 +7364,7 @@
       <c r="A30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Custom / Made-to-Order",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7282,7 +7373,7 @@
       <c r="A31" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$D$3:$D$152,"Other",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7293,10 +7384,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7304,7 +7395,7 @@
       <c r="A36" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="11" t="n">
+      <c r="B36" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$E$3:$E$152,"North America",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7313,7 +7404,7 @@
       <c r="A37" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$E$3:$E$152,"Europe",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7322,7 +7413,7 @@
       <c r="A38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$E$3:$E$152,"Asia Pacific",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7331,7 +7422,7 @@
       <c r="A39" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$E$3:$E$152,"Other",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7342,10 +7433,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7353,7 +7444,7 @@
       <c r="A46" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="11" t="n">
+      <c r="B46" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$F$3:$F$152,"Etsy",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7362,7 +7453,7 @@
       <c r="A47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$F$3:$F$152,"Website",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7371,7 +7462,7 @@
       <c r="A48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B48" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$F$3:$F$152,"Amazon",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7380,7 +7471,7 @@
       <c r="A49" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B49" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$F$3:$F$152,"Instagram",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7389,7 +7480,7 @@
       <c r="A50" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B50" s="17" t="n">
         <f aca="false">SUMIFS('Sales Transactions'!$I$3:$I$152,'Sales Transactions'!$F$3:$F$152,"Other",'Sales Transactions'!$J$3:$J$152,$B$3)</f>
         <v>0</v>
       </c>
@@ -7446,7 +7537,7 @@
       <c r="A4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="23" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7454,7 +7545,7 @@
       <c r="A5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="23" t="s">
         <v>70</v>
       </c>
     </row>
@@ -7462,7 +7553,7 @@
       <c r="A6" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7470,7 +7561,7 @@
       <c r="A7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="23" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7478,7 +7569,7 @@
       <c r="A8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="23" t="s">
         <v>76</v>
       </c>
     </row>
